--- a/saidas/tabelas/tabelas_completas_cat_saude_campos.xlsx
+++ b/saidas/tabelas/tabelas_completas_cat_saude_campos.xlsx
@@ -43,13 +43,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +63,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,12 +71,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,32 +455,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>apoio_ou_outra</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>multiprofissional</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nao_classificado</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>total</t>
         </is>
@@ -665,17 +677,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>agente_causador</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -852,17 +864,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>natureza_lesao</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1039,17 +1051,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>parte_corpo_atingida</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1188,7 +1200,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mao (Exceto Punho ou Dedos)</t>
+          <t>Braco (Entre O Punho</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1201,7 +1213,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Braco (Entre O Punho</t>
+          <t>Mao (Exceto Punho ou Dedos)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1226,17 +1238,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cid10</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1310,7 +1322,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>S93 Entorse e Dist</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1323,7 +1335,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S93 Entorse e Dist</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1349,7 +1361,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">S80 </t>
+          <t>Y28 Outr Locais Es</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1362,7 +1374,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y28 Outr Locais Es</t>
+          <t xml:space="preserve">S80 </t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1375,7 +1387,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S61 Ferim do Punho</t>
+          <t>S40 Contusao do Om</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1388,7 +1400,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S40 Contusao do Om</t>
+          <t>S61 Ferim do Punho</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1413,17 +1425,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cnae</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1600,17 +1612,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>emitente_cat</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1683,17 +1695,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>origem_cadastramento_cat</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1740,17 +1752,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>filiacao_segurado</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1797,17 +1809,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>indica_obito_acidente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1854,32 +1866,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_validos</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mediana</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>p25</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>p75</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_total</t>
         </is>
@@ -2060,12 +2072,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -2946,67 +2958,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cbo_codigo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>cid10_codigo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>cnae_classe</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>idade</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tipo_acidente</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>agente_causador</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>natureza_lesao</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>parte_corpo_atingida</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>emitente_cat</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>data_emissao_cat</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>origem_cadastramento_cat</t>
         </is>
@@ -3355,27 +3367,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>periodo_pandemia</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>meses_no_periodo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>media_mensal</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_agente_infeccioso</t>
         </is>
@@ -3453,12 +3465,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pct_agente_infeccioso</t>
         </is>
@@ -3543,17 +3555,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_saude_principal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
@@ -3679,17 +3691,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cbo_codigo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cbo_titulo_oficial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -4085,32 +4097,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>outras_ocupacoes_total</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>outras_ocupacoes_em_cnae_saude</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>nao_classificados_total</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nao_classificados_em_cnae_saude</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>saude_principal_fora_cnae_saude</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>saude_principal_pct_em_cnae_saude</t>
         </is>
@@ -4151,12 +4163,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>etapa</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -4277,22 +4289,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>grupo4</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mediana</t>
         </is>
@@ -4393,17 +4405,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>categoria_profissional</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -4580,17 +4592,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>categoria_profissional</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -4663,22 +4675,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cbo_codigo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cbo_titulo_oficial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>categoria_profissional</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -5319,22 +5331,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>cbo_codigo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cbo_titulo_oficial</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>categoria_profissional</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
@@ -5635,37 +5647,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Demais profissões da saúde</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Diagnóstico e laboratório – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – enfermeiros</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -5736,37 +5748,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>faixa_etaria</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Demais profissões da saúde</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Diagnóstico e laboratório – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – enfermeiros</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -5937,37 +5949,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tipo_acidente</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Demais profissões da saúde</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Diagnóstico e laboratório – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – enfermeiros</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Enfermagem – técnicos e auxiliares</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Medicina</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
